--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$86</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4057" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2742" uniqueCount="313">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -784,111 +784,68 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
+    <t>Entrées Acte (procedure), Simple observation (observation) et/ou Références externes (act)</t>
+  </si>
+  <si>
+    <t>Section.entry.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.entry.realmCode</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.displayable</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.root</t>
+  </si>
+  <si>
+    <t>Section.entry.typeId.extension</t>
+  </si>
+  <si>
+    <t>Section.entry.templateId</t>
+  </si>
+  <si>
+    <t>Section.entry.typeCode</t>
+  </si>
+  <si>
+    <t>COMP</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipEntry|3.0.0</t>
+  </si>
+  <si>
+    <t>Entry.typeCode</t>
+  </si>
+  <si>
+    <t>Section.entry.contextConductionInd</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>Entry.contextConductionInd</t>
+  </si>
+  <si>
+    <t>Section.entry.act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-references-externes|0.1.0}
 </t>
   </si>
   <si>
-    <t>Section.entry:frActe</t>
-  </si>
-  <si>
-    <t>frActe</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry.typeCode</t>
-  </si>
-  <si>
-    <t>COMP</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-xActRelationshipEntry|3.0.0</t>
-  </si>
-  <si>
-    <t>Entry.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>Entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.act</t>
-  </si>
-  <si>
-    <t>Section.entry.act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act
-</t>
+    <t>Entrée référence Externe</t>
   </si>
   <si>
     <t>Entry.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.encounter</t>
   </si>
   <si>
     <t>Section.entry.encounter</t>
@@ -901,20 +858,17 @@
     <t>Entry.encounter</t>
   </si>
   <si>
-    <t>Section.entry:frActe.observation</t>
-  </si>
-  <si>
     <t>Section.entry.observation</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-simple-observation|0.1.0}
 </t>
   </si>
   <si>
+    <t>Entrée Simple observation</t>
+  </si>
+  <si>
     <t>Entry.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frActe.observationMedia</t>
   </si>
   <si>
     <t>Section.entry.observationMedia</t>
@@ -927,9 +881,6 @@
     <t>Entry.observationMedia</t>
   </si>
   <si>
-    <t>Section.entry:frActe.organizer</t>
-  </si>
-  <si>
     <t>Section.entry.organizer</t>
   </si>
   <si>
@@ -940,9 +891,6 @@
     <t>Entry.organizer</t>
   </si>
   <si>
-    <t>Section.entry:frActe.procedure</t>
-  </si>
-  <si>
     <t>Section.entry.procedure</t>
   </si>
   <si>
@@ -956,9 +904,6 @@
     <t>Entry.procedure</t>
   </si>
   <si>
-    <t>Section.entry:frActe.regionOfInterest</t>
-  </si>
-  <si>
     <t>Section.entry.regionOfInterest</t>
   </si>
   <si>
@@ -969,9 +914,6 @@
     <t>Entry.regionOfInterest</t>
   </si>
   <si>
-    <t>Section.entry:frActe.substanceAdministration</t>
-  </si>
-  <si>
     <t>Section.entry.substanceAdministration</t>
   </si>
   <si>
@@ -982,9 +924,6 @@
     <t>Entry.substanceAdministration</t>
   </si>
   <si>
-    <t>Section.entry:frActe.supply</t>
-  </si>
-  <si>
     <t>Section.entry.supply</t>
   </si>
   <si>
@@ -993,156 +932,6 @@
   </si>
   <si>
     <t>Entry.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation</t>
-  </si>
-  <si>
-    <t>frSimpleObservation</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-simple-observation|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée Simple observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.procedure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Procedure
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frSimpleObservation.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes</t>
-  </si>
-  <si>
-    <t>frReferencesExternes</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Act {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-references-externes|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée référence interne</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.procedure</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frReferencesExternes.supply</t>
   </si>
   <si>
     <t>Section.component</t>
@@ -1515,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK129"/>
+  <dimension ref="A1:AK86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.82421875" customWidth="true" bestFit="true"/>
@@ -6890,7 +6679,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>246</v>
       </c>
@@ -6920,7 +6709,9 @@
       <c r="K53" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="L53" s="2"/>
+      <c r="L53" t="s" s="2">
+        <v>248</v>
+      </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6959,14 +6750,16 @@
         <v>75</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="AC53" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>246</v>
@@ -6992,20 +6785,20 @@
         <v>249</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E54" s="2"/>
+      <c r="E54" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7017,10 +6810,12 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
+      <c r="M54" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7046,13 +6841,11 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -7070,13 +6863,13 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>246</v>
+        <v>90</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>75</v>
@@ -7090,23 +6883,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E55" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7118,11 +6909,11 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7149,11 +6940,13 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7171,13 +6964,13 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
@@ -7191,10 +6984,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7205,7 +6998,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7217,11 +7010,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7272,19 +7065,19 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>75</v>
@@ -7292,16 +7085,18 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E57" s="2"/>
+      <c r="E57" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
@@ -7318,11 +7113,11 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7349,13 +7144,11 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7373,7 +7166,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7385,7 +7178,7 @@
         <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>75</v>
@@ -7393,17 +7186,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>81</v>
@@ -7421,11 +7214,11 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7452,11 +7245,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -7474,7 +7269,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7494,17 +7289,17 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>81</v>
@@ -7522,11 +7317,11 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7577,7 +7372,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7597,20 +7392,20 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E60" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F60" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>76</v>
@@ -7625,11 +7420,11 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7638,7 +7433,7 @@
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>75</v>
@@ -7680,7 +7475,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7700,17 +7495,17 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E61" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F61" t="s" s="2">
         <v>76</v>
@@ -7728,11 +7523,11 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7741,7 +7536,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>75</v>
@@ -7783,7 +7578,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7803,23 +7598,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E62" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -7831,11 +7624,11 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7886,13 +7679,13 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>75</v>
@@ -7906,10 +7699,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7920,7 +7713,7 @@
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>75</v>
@@ -7932,16 +7725,14 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
-        <v>75</v>
+        <v>259</v>
       </c>
       <c r="Q63" s="2"/>
       <c r="R63" t="s" s="2">
@@ -7963,13 +7754,11 @@
         <v>75</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y63" s="2"/>
       <c r="Z63" t="s" s="2">
-        <v>75</v>
+        <v>260</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -7987,13 +7776,13 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>126</v>
+        <v>261</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>75</v>
@@ -8007,10 +7796,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8033,18 +7822,18 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="S64" t="s" s="2">
         <v>75</v>
@@ -8062,11 +7851,13 @@
         <v>75</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y64" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z64" t="s" s="2">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
@@ -8084,7 +7875,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8104,10 +7895,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8130,9 +7921,11 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L65" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8141,7 +7934,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>75</v>
@@ -8183,7 +7976,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8203,10 +7996,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8229,7 +8022,7 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8282,7 +8075,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8302,10 +8095,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8328,9 +8121,11 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L67" s="2"/>
+        <v>273</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8381,7 +8176,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8401,10 +8196,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8427,7 +8222,7 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8480,7 +8275,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -8500,10 +8295,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8526,7 +8321,7 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8579,7 +8374,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -8599,10 +8394,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8625,9 +8420,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L70" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8678,7 +8475,7 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -8698,10 +8495,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8724,11 +8521,9 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="L71" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="L71" s="2"/>
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8779,7 +8574,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -8799,10 +8594,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8825,7 +8620,7 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -8878,7 +8673,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8898,10 +8693,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8924,7 +8719,7 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
@@ -8977,7 +8772,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -8997,10 +8792,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9011,7 +8806,7 @@
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>75</v>
@@ -9023,12 +8818,16 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L74" s="2"/>
+        <v>296</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>297</v>
+      </c>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -9076,13 +8875,13 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>75</v>
@@ -9096,23 +8895,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>315</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>75</v>
@@ -9124,10 +8923,12 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>247</v>
+        <v>86</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -9153,13 +8954,11 @@
         <v>75</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>75</v>
@@ -9177,13 +8976,13 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>246</v>
+        <v>90</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>75</v>
@@ -9197,23 +8996,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>252</v>
+        <v>300</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E76" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>75</v>
@@ -9225,11 +9022,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9256,11 +9053,13 @@
         <v>75</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>75</v>
@@ -9278,13 +9077,13 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>75</v>
@@ -9298,10 +9097,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9312,7 +9111,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
@@ -9324,11 +9123,11 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9379,19 +9178,19 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -9399,16 +9198,18 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F78" t="s" s="2">
         <v>81</v>
       </c>
@@ -9425,11 +9226,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9456,13 +9257,11 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y78" s="2"/>
       <c r="Z78" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -9480,7 +9279,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -9492,7 +9291,7 @@
         <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>75</v>
@@ -9500,17 +9299,17 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>258</v>
+        <v>303</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
@@ -9528,11 +9327,11 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9559,11 +9358,13 @@
         <v>75</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -9581,7 +9382,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9601,17 +9402,17 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -9629,11 +9430,11 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9684,7 +9485,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -9704,20 +9505,20 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>262</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F81" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>76</v>
@@ -9732,11 +9533,11 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9745,7 +9546,7 @@
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>75</v>
@@ -9787,7 +9588,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -9807,17 +9608,17 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>323</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>264</v>
+        <v>306</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>76</v>
@@ -9835,11 +9636,11 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9848,7 +9649,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>75</v>
@@ -9890,7 +9691,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9910,23 +9711,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E83" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>75</v>
@@ -9938,11 +9737,11 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9993,13 +9792,13 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>75</v>
@@ -10013,10 +9812,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10027,7 +9826,7 @@
         <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>75</v>
@@ -10039,11 +9838,11 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>123</v>
+        <v>309</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10052,7 +9851,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>75</v>
+        <v>259</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>75</v>
@@ -10094,13 +9893,13 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>126</v>
+        <v>308</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>75</v>
@@ -10114,10 +9913,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>326</v>
+        <v>310</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>270</v>
+        <v>310</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10140,18 +9939,18 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
-        <v>271</v>
+        <v>75</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>75</v>
+        <v>263</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>75</v>
@@ -10169,11 +9968,13 @@
         <v>75</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y85" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z85" t="s" s="2">
-        <v>272</v>
+        <v>75</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10191,7 +9992,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>273</v>
+        <v>310</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10211,10 +10012,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>327</v>
+        <v>311</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10222,7 +10023,7 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>76</v>
@@ -10237,7 +10038,7 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10248,7 +10049,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>276</v>
+        <v>75</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>75</v>
@@ -10290,10 +10091,10 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>277</v>
+        <v>311</v>
       </c>
       <c r="AG86" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
         <v>76</v>
@@ -10308,4327 +10109,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E91" s="2"/>
-      <c r="F91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y97" s="2"/>
-      <c r="Z97" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L98" s="2"/>
-      <c r="M98" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L99" s="2"/>
-      <c r="M99" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E100" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L100" s="2"/>
-      <c r="M100" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y100" s="2"/>
-      <c r="Z100" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E101" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L101" s="2"/>
-      <c r="M101" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E102" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L102" s="2"/>
-      <c r="M102" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E103" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L103" s="2"/>
-      <c r="M103" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
-      <c r="P103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L104" s="2"/>
-      <c r="M104" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
-      <c r="P104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
-      <c r="P105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L106" s="2"/>
-      <c r="M106" s="2"/>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y106" s="2"/>
-      <c r="Z106" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L107" s="2"/>
-      <c r="M107" s="2"/>
-      <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="M108" s="2"/>
-      <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
-      <c r="P108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
-      <c r="N109" s="2"/>
-      <c r="O109" s="2"/>
-      <c r="P109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L110" s="2"/>
-      <c r="M110" s="2"/>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="L112" s="2"/>
-      <c r="M112" s="2"/>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
-      <c r="N114" s="2"/>
-      <c r="O114" s="2"/>
-      <c r="P114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="L115" s="2"/>
-      <c r="M115" s="2"/>
-      <c r="N115" s="2"/>
-      <c r="O115" s="2"/>
-      <c r="P115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M117" s="2"/>
-      <c r="N117" s="2"/>
-      <c r="O117" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y118" s="2"/>
-      <c r="Z118" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L120" s="2"/>
-      <c r="M120" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E121" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L121" s="2"/>
-      <c r="M121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y121" s="2"/>
-      <c r="Z121" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E122" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L123" s="2"/>
-      <c r="M123" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L124" s="2"/>
-      <c r="M124" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E125" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L125" s="2"/>
-      <c r="M125" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L126" s="2"/>
-      <c r="M126" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L127" s="2"/>
-      <c r="M127" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="L129" s="2"/>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK129">
+  <autoFilter ref="A1:AK86">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14638,7 +10120,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI128">
+  <conditionalFormatting sqref="A2:AI85">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-education-du-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
